--- a/out/Attention_Base_repeat_2_000001.xlsx
+++ b/out/Attention_Base_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-3.997815127472859e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.01721343121673911</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.03447280053031293</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.06650458816949664</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC45" t="n">
-        <v>-1.008381460269447e-05</v>
+        <v>0.1503125648032662</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.00598888341378098</v>
+        <v>0.02045718412648821</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.005998967228383641</v>
+        <v>0.1246381556901587</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.004148456709721048</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.006007383252454689</v>
+        <v>0.1124485470426455</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.00277702551335649</v>
+        <v>0.00359188650882811</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0004345760678601218</v>
+        <v>0.1154797786514673</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001312678564582826</v>
+        <v>0.001753444531976468</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0005933615407709731</v>
+        <v>0.1153910713691376</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0005802275309094079</v>
+        <v>0.0008342235435506434</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0007487384910971159</v>
+        <v>0.1153042190055349</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0001591141378954973</v>
+        <v>0.0003446140075095411</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.001012761931567336</v>
+        <v>0.1151582599755391</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0002010897315383542</v>
+        <v>0.0002373048478682023</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0007702783064931864</v>
+        <v>0.1152879391059952</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>6.117955216796523e-05</v>
+        <v>9.61530627153065e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.1348825055873002</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0008492624793268042</v>
+        <v>0.1152426769818787</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>3.152915667574978e-05</v>
+        <v>4.711738566636162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0008475531870295527</v>
+        <v>0.1152413221421279</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.946436562573218e-06</v>
+        <v>1.546969937155907e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0008734461702266708</v>
+        <v>0.1152249393480336</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.929085771702397e-07</v>
+        <v>6.452665226717778e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.206964148813839</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0008750011102874997</v>
+        <v>0.115221826699907</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-2.296853236071846e-06</v>
+        <v>6.467173218827975e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0008803190083242953</v>
+        <v>0.1152166545182723</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-3.935041667349865e-06</v>
+        <v>-2.335871922010791e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0008859359509228961</v>
+        <v>0.1152113294859275</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.533250587006911e-06</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1152059684834257</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>4.806964148813838</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115200823909492</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151954961151693</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955758261138</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955678550194</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957272769085</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151959823519313</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151956953925306</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151958309011366</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957671323807</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957272769085</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195456259697</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151953765487522</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151954243753189</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195543941736</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955279995471</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195543941736</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955279995471</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957352480029</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151959504675535</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151958627855144</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151958149589477</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151958627855144</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151956794503417</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151956874214362</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151956953925306</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957033636251</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151957432190974</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151958069878533</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151959185831756</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151959664097424</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151959265542701</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.11519585481442</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151959743808368</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151958149589477</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955837972083</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955678550194</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955519128304</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151954323464134</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151953924909411</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151956714792473</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151956555370584</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955917683027</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151954881440748</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151953685776577</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC122" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151954881440748</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC123" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955359706415</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC124" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.115195631623775</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC125" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955120573582</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.7348825055873003</v>
       </c>
       <c r="JC126" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1151955200284526</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_2_000001.xlsx
+++ b/out/Attention_Base_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.418340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-4.491324963280931e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.01933823420918107</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.03872829202347226</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.07471382583829168</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC45" t="n">
-        <v>-1.008381460269447e-05</v>
+        <v>0.1688686050749267</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.00598888341378098</v>
+        <v>0.02298290066382671</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.005998967228383641</v>
+        <v>0.1400243423161548</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.00466148943359522</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.006007383252454689</v>
+        <v>0.1263303780375798</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.00277702551335649</v>
+        <v>0.004035769796143681</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0004345760678601218</v>
+        <v>0.1297363038337959</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001312678564582826</v>
+        <v>0.001970450027562736</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0005933615407709731</v>
+        <v>0.1296372664330257</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0005802275309094079</v>
+        <v>0.0009377901432722595</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0007487384910971159</v>
+        <v>0.1295403128621315</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0001591141378954973</v>
+        <v>0.0003874806931436727</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.001012761931567336</v>
+        <v>0.1293769590436451</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0002010897315383542</v>
+        <v>0.0002674000359792211</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0007702783064931864</v>
+        <v>0.1295233658368012</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>6.117955216796523e-05</v>
+        <v>0.0001083945161649296</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0008492624793268042</v>
+        <v>0.1294731036888151</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>3.152915667574978e-05</v>
+        <v>5.379910177743361e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0008475531870295527</v>
+        <v>0.1294722131114961</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.946436562573218e-06</v>
+        <v>1.809401980381023e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0008734461702266708</v>
+        <v>0.1294543893796587</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.929085771702397e-07</v>
+        <v>7.597931749389555e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0008750011102874997</v>
+        <v>0.1294515132932863</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-2.296853236071846e-06</v>
+        <v>1.211389054071076e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0008803190083242953</v>
+        <v>0.1294463159223939</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-3.935041667349865e-06</v>
+        <v>-1.80304630641295e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0008859359509228961</v>
+        <v>0.12944092588358</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.533250587006911e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294354919896026</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294303474156689</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250196213461</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250594768184</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250993322907</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250913611963</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252507830854</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294255058581082</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252587541798</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252188987075</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425226869802</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252587541798</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294253544073135</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252906385576</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252507830854</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425226869802</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294249797658739</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294249000549291</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294249478814958</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250674479129</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425051505724</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250674479129</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425051505724</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251073033852</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251073033852</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251073033852</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252587541798</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294254739737304</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294253862916913</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294253384651246</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294253862916913</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252029565186</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252109276131</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252188987075</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425226869802</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425226869802</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294252667252743</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294253304940302</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294254420893525</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294254899159193</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425450060447</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294253783205969</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294254978870137</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294253384651246</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251073033852</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250594768184</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250913611963</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250754190073</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294249558525903</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129424915997118</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250594768184</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251949854242</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251790432353</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251152744796</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250116502517</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294248920838346</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC122" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250116502517</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC123" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250594768184</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC124" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294251551299519</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC125" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.129425035563535</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC126" t="n">
-        <v>-0.0008916648656791076</v>
+        <v>0.1294250435346295</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_2_000001.xlsx
+++ b/out/Attention_Base_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.008365846239030361</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.4399999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0007459362968802452</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.2299999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.001995314843952656</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.612576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003925091587007046</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.612576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.004112131893634796</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.612576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001837912015616894</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.612576626421732</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.003152167424559593</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.612576626421732</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.004225765354931355</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.612576626421732</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.004279755987226963</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.005446059629321098</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.412576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.005755772814154625</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.412576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.006445256061851978</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.412576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.006205294281244278</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.412576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.005061041563749313</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003605779260396957</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002191814593970776</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001713225618004799</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001288636587560177</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0009186817333102226</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.00104353204369545</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001255443319678307</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001195743680000305</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0008550994098186493</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0003832457587122917</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0002516834065318108</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0002295235171914101</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0002837274223566055</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0005530770868062973</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0005983449518680573</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>4.004500806331635e-05</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>4.337448626756668e-05</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-6.244238466024399e-05</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0001577790826559067</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0004453975707292557</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0007926812395453453</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0009633870795369148</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001013834029436111</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0009668758139014244</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0004418455064296722</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9168981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0003947392106056213</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001613174565136433</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.003188105765730143</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-4.491324963280931e-05</v>
+        <v>-1.832464563928079e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.01933823420918107</v>
+        <v>0.007889953300800185</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.004251064732670784</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.03872829202347226</v>
+        <v>0.01580117777179286</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.07471382583829168</v>
+        <v>0.03048388960583396</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.00693263066932559</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1688686050749267</v>
+        <v>0.06889896671024384</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.02298290066382671</v>
+        <v>0.00937620908896813</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01070600561797619</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1400243423161548</v>
+        <v>0.05712971148819337</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.00466148943359522</v>
+        <v>0.001898719333956945</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01260368153452873</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1263303780375798</v>
+        <v>0.05153961946045398</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.004035769796143681</v>
+        <v>0.001643811630141548</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01685965061187744</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1297363038337959</v>
+        <v>0.05292642706298525</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001970450027562736</v>
+        <v>0.0008007204045799818</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01663367636501789</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1296372664330257</v>
+        <v>0.052883056390716</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0009377901432722595</v>
+        <v>0.0003798668479977473</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01812321320176125</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1295403128621315</v>
+        <v>0.05284051900103851</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0003874806931436727</v>
+        <v>0.0001553325384757131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01854230836033821</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1293769590436451</v>
+        <v>0.05277087536944775</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0002674000359792211</v>
+        <v>0.0001061206945637616</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01972804963588715</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1295233658368012</v>
+        <v>0.05282763904710929</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001083945161649296</v>
+        <v>4.138866570383483e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01779851317405701</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1294731036888151</v>
+        <v>0.05280417488827859</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>5.379910177743361e-05</v>
+        <v>1.905417799985921e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01805534772574902</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1294722131114961</v>
+        <v>0.05280084623303218</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>1.809401980381023e-05</v>
+        <v>4.447553556104185e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0205000527203083</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1294543893796587</v>
+        <v>0.05279065885715792</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.597931749389555e-06</v>
+        <v>1.536993520230006e-07</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.02074905298650265</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1294515132932863</v>
+        <v>0.05278650816550106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.211389054071076e-06</v>
+        <v>-2.741313071246881e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.02190398052334785</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.1294463159223939</v>
+        <v>0.05278143132175273</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-1.80304630641295e-06</v>
+        <v>-3.934348768804317e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.02088714204728603</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.12944092588358</v>
+        <v>0.05277626942443685</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.616484440191926e-06</v>
+        <v>-4.538828146730642e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.02026137337088585</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1294354919896026</v>
+        <v>0.05277105305326101</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01987816020846367</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1294303474156689</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01877878233790398</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01877971552312374</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1294250196213461</v>
+        <v>0.05276572514415463</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01829944923520088</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1294250594768184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01906741410493851</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1294250993322907</v>
+        <v>0.05276580485509918</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01828181371092796</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1294250913611963</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01893739774823189</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1294252507830854</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01787709072232246</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01929186657071114</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1294255058581082</v>
+        <v>0.05276621138091665</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01947159133851528</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1294252587541798</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01904444023966789</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1294252188987075</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01992129534482956</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01971520110964775</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.129425226869802</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01924891024827957</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01622991636395454</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1294252587541798</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01898559927940369</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1294253544073135</v>
+        <v>0.05276605993012199</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02082284167408943</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1294252906385576</v>
+        <v>0.05276599616136612</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02119883894920349</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1294252507830854</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01951563730835915</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.129425226869802</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01961842551827431</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1294249797658739</v>
+        <v>0.05276568528868235</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01984319649636745</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1294249000549291</v>
+        <v>0.05276560557773756</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01966389268636703</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1294249478814958</v>
+        <v>0.05276565340430429</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01992102712392807</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1294250674479129</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01917116716504097</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.129425051505724</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01907926797866821</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1294250674479129</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01880114153027534</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.129425051505724</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01887941174209118</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1294251073033852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01917518116533756</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1294251073033852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01754176989197731</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1294251073033852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01900871843099594</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1294252587541798</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01747722923755646</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1294254739737304</v>
+        <v>0.05276617949653883</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01932363957166672</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1294253862916913</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01908038556575775</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1294253384651246</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01834144815802574</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1294253862916913</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01868030801415443</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1294252029565186</v>
+        <v>0.05276590847932711</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01847036927938461</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1294252109276131</v>
+        <v>0.05276591645042156</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01799839735031128</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1294252188987075</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0183437243103981</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.129425226869802</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01808467879891396</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.129425226869802</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01667957380414009</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1294252667252743</v>
+        <v>0.05276597224808275</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01732810400426388</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1294253304940302</v>
+        <v>0.05276603601683862</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.01738287508487701</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1294254420893525</v>
+        <v>0.052766147612161</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01804589852690697</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1294254899159193</v>
+        <v>0.05276619543872774</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01737954095005989</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.129425450060447</v>
+        <v>0.05276615558325546</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01726995967328548</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1294253783205969</v>
+        <v>0.05276608384340536</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01713457703590393</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1294254978870137</v>
+        <v>0.05276620340982219</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01624714583158493</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1294253384651246</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01677617244422436</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1294251073033852</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01667497865855694</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1294250594768184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01714454218745232</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1294250913611963</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01666988618671894</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01688073575496674</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01647515408694744</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1294250754190073</v>
+        <v>0.05276578094181581</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01586728915572166</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1294249558525903</v>
+        <v>0.05276566137539875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01591641455888748</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.129424915997118</v>
+        <v>0.05276562151992647</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.01581718027591705</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1294250594768184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.01610400155186653</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1294251949854242</v>
+        <v>0.05276590050823265</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01618494279682636</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1294251790432353</v>
+        <v>0.05276588456604374</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01571542955935001</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01538039278239012</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1294251152744796</v>
+        <v>0.05276582079728809</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01447710581123829</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1294250116502517</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.01419413555413485</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1294248920838346</v>
+        <v>0.0527655976066431</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01504205819219351</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1294250116502517</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01485493499785662</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1294250594768184</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01522867195308208</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1294251551299519</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01481461990624666</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.09000000000000052</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.129425035563535</v>
+        <v>0.05276574108634353</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01421155873686075</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1294250435346295</v>
+        <v>0.05276574905743799</v>
       </c>
     </row>
   </sheetData>
